--- a/projects/ai-core/doc/data/res_syn_area.xlsx
+++ b/projects/ai-core/doc/data/res_syn_area.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t xml:space="preserve">Synthesis Cell Area — Baseline (top_NxN) vs Square (top_NxN_sqr), ASAP7 RVT/TT</t>
   </si>
@@ -74,7 +74,13 @@
     <t xml:space="preserve">64 / 256</t>
   </si>
   <si>
-    <t xml:space="preserve">top regs (sel_acc, 2 flops)</t>
+    <t xml:space="preserve">icg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 / 288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">top glue (sel_acc regs + grid fan-out)</t>
   </si>
   <si>
     <t xml:space="preserve">Baseline total </t>
@@ -104,7 +110,7 @@
     <t xml:space="preserve">pe_sqr</t>
   </si>
   <si>
-    <t xml:space="preserve">top regs (sel_acc+const, 46 flops)</t>
+    <t xml:space="preserve">top glue (sel_acc/const regs + grid fan-out)</t>
   </si>
   <si>
     <t xml:space="preserve">Square total </t>
@@ -173,7 +179,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -188,14 +194,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEEEEE"/>
-        <bgColor rgb="FFEFEFEF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFEFEF"/>
-        <bgColor rgb="FFEEEEEE"/>
+        <fgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -245,7 +245,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -273,16 +273,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -322,12 +322,12 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFEFEFEF"/>
-      <rgbColor rgb="FFEEEEEE"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -370,18 +370,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:I23"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:I25"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.98"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="10" style="1" width="8.67"/>
   </cols>
   <sheetData>
@@ -423,7 +423,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
@@ -435,7 +435,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
@@ -461,7 +461,7 @@
         <v>9.22914</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="n">
         <v>2</v>
       </c>
@@ -487,7 +487,7 @@
         <v>5578.8912</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="n">
         <v>3</v>
       </c>
@@ -513,7 +513,7 @@
         <v>8039.76192</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="n">
         <v>4</v>
       </c>
@@ -539,7 +539,7 @@
         <v>962289.3312</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="n">
         <v>5</v>
       </c>
@@ -547,319 +547,380 @@
         <v>17</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>20.9952</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>75.58272</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E10" s="7" t="n">
         <v>0.75816</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F10" s="7" t="n">
         <v>0.75816</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="7" t="n">
-        <v>0.75816</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>0.75816</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9" t="n">
-        <v>247391.64666</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>975917.97162</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="H10" s="7" t="n">
+        <v>10.1768400000001</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>38.1704410000239</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>9.46242</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>4.16988</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>5.29254</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>9.46242</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>9.46242</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="9" t="n">
+        <v>247422.06054</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>976030.966621</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>4.06782</v>
+        <v>9.46242</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0</v>
+        <v>4.16988</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.06782</v>
+        <v>5.29254</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.06782</v>
+        <v>9.46242</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>4.06782</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>9.46242</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="n">
         <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>394.78266</v>
+        <v>4.06782</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>97.04448</v>
+        <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>297.73818</v>
+        <v>4.06782</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>3158.26128</v>
+        <v>4.06782</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>6316.52256</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>4.06782</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="n">
         <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>349.59924</v>
+        <v>394.78266</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>97.04448</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>252.55476</v>
+        <v>297.73818</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>2796.79392</v>
+        <v>3158.26128</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>5593.58784</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>6316.52256</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1890.26784</v>
+        <v>349.59924</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>150.11568</v>
+        <v>97.04448</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1740.15216</v>
+        <v>252.55476</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>15122.14272</v>
+        <v>2796.79392</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>30244.28544</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>5593.58784</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="n">
         <v>11</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1699.8093</v>
+        <v>1890.26784</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>150.11568</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1549.69362</v>
+        <v>1740.15216</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>13598.4744</v>
+        <v>15122.14272</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>27196.9488</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30244.28544</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>3264.18498</v>
+        <v>1699.8093</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>327.52512</v>
+        <v>150.11568</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>2936.65986</v>
+        <v>1549.69362</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>208907.83872</v>
+        <v>13598.4744</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>835631.35488</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>27196.9488</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="n">
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>3264.18498</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>327.52512</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>2936.65986</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>208907.83872</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>835631.35488</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>20.9952</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>75.58272</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E21" s="7" t="n">
         <v>17.43768</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F21" s="7" t="n">
         <v>17.43768</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="7" t="n">
-        <v>17.43768</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>17.43768</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="9" t="n">
-        <v>243614.47896</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>905013.66744</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="11" t="n">
-        <v>0.984732032180573</v>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>0.927346041120341</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="10" t="s">
+      <c r="H21" s="7" t="n">
+        <v>28.7809199999901</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>56.7745209999848</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="8" t="s">
         <v>30</v>
       </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="9" t="n">
+        <v>243646.8174</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>905128.587001</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="12" t="n">
-        <v>-0.0152679678194272</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>-0.0726539588796593</v>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="11" t="n">
+        <v>0.984741687415582</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>0.927356424084102</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="12" t="n">
+        <v>-0.0152583125844176</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>-0.0726435759158981</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B12:I12"/>
     <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B25:G25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/projects/ai-core/doc/data/res_syn_area.xlsx
+++ b/projects/ai-core/doc/data/res_syn_area.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="48">
   <si>
-    <t xml:space="preserve">Synthesis Cell Area — Baseline / Square / BFP / Square-BFP (top_NxN[_sqr][_bfp]), ASAP7 RVT/TT (analytic from 2x2)</t>
+    <t xml:space="preserve">Synthesis Cell Area — Baseline / Square / BFP / Square-BFP, ASAP7 RVT/TT (analytic from 2x2)</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -409,7 +409,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:I58"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.98"/>

--- a/projects/ai-core/doc/data/res_syn_area.xlsx
+++ b/projects/ai-core/doc/data/res_syn_area.xlsx
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="48">
-  <si>
-    <t xml:space="preserve">Synthesis Cell Area — Baseline / Square / BFP / Square-BFP, ASAP7 RVT/TT (analytic from 2x2)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="54">
+  <si>
+    <t xml:space="preserve">Synthesis Cell Area — Baseline / Square / BFP / Square-BFP / Bit-Plane BFP, ASAP7 RVT/TT (analytic from 2x2)</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -155,6 +155,18 @@
     <t xml:space="preserve">Square-BFP total </t>
   </si>
   <si>
+    <t xml:space="preserve">Bit-Plane BFP — top_NxN_bpl_bfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disp_array_b_bpl_bfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pe_bpl_bfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bit-Plane BFP total </t>
+  </si>
+  <si>
     <t xml:space="preserve">Square / Baseline (× area) </t>
   </si>
   <si>
@@ -165,6 +177,12 @@
   </si>
   <si>
     <t xml:space="preserve">Square-BFP / BFP (× area) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bit-Plane BFP / Baseline (× area) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bit-Plane BFP / BFP (× area) </t>
   </si>
 </sst>
 </file>
@@ -290,8 +308,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -408,1230 +430,1523 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:I58"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B1:I71"/>
+  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>8.87922</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <v>3.412</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="8" t="n">
         <v>5.4672</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="8" t="n">
         <v>8.879</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="8" t="n">
         <v>8.879</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="D6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>277.73442</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>97.044</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>180.6904</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="8" t="n">
         <v>2221.875</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="8" t="n">
         <v>4443.751</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="6" t="n">
+      <c r="D7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>466.32672</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>97.044</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="8" t="n">
         <v>369.2827</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="8" t="n">
         <v>3730.614</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="8" t="n">
         <v>7461.228</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>3816.51912</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>345.721</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>3470.7981</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>244257.224</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="8" t="n">
         <v>977028.895</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>0.26244</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="8" t="n">
         <v>0.2624</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="8" t="n">
         <v>16.796</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="8" t="n">
         <v>67.185</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>0.26244</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>0.2624</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="8" t="n">
         <v>4.199</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="8" t="n">
         <v>8.398</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>1.77876</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="8" t="n">
         <v>1.7788</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="8" t="n">
         <v>1.779</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="8" t="n">
         <v>1.779</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="9" t="n">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="10" t="n">
         <v>250241.366</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="10" t="n">
         <v>989020.114</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>9.7686</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="8" t="n">
         <v>4.17</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="8" t="n">
         <v>5.5986</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="8" t="n">
         <v>9.769</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="8" t="n">
         <v>9.769</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>3.74706</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="8" t="n">
         <v>3.7471</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="8" t="n">
         <v>3.747</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="8" t="n">
         <v>3.747</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="6" t="n">
+      <c r="D17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="7" t="n">
         <v>366.11838</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="8" t="n">
         <v>97.044</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="8" t="n">
         <v>269.0744</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H17" s="8" t="n">
         <v>2928.947</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="8" t="n">
         <v>5857.894</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="6" t="n">
+      <c r="D18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="7" t="n">
         <v>332.68644</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="8" t="n">
         <v>97.044</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="8" t="n">
         <v>235.6424</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="8" t="n">
         <v>2661.492</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I18" s="8" t="n">
         <v>5322.983</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="6" t="n">
+      <c r="D19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="7" t="n">
         <v>1962.23472</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="8" t="n">
         <v>150.116</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="8" t="n">
         <v>1812.1187</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H19" s="8" t="n">
         <v>15697.878</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="8" t="n">
         <v>31395.756</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="6" t="n">
+      <c r="D20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="7" t="n">
         <v>1753.6824</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="8" t="n">
         <v>150.116</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="8" t="n">
         <v>1603.5664</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H20" s="8" t="n">
         <v>14029.459</v>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="I20" s="8" t="n">
         <v>28058.918</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>3320.3034</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="8" t="n">
         <v>327.525</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="8" t="n">
         <v>2992.7784</v>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="H21" s="8" t="n">
         <v>212499.418</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="I21" s="8" t="n">
         <v>849997.67</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>0.26244</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="8" t="n">
         <v>0.2624</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H22" s="8" t="n">
         <v>16.796</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="8" t="n">
         <v>67.185</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>0.26244</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="8" t="n">
         <v>0.2624</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="H23" s="8" t="n">
         <v>4.199</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="8" t="n">
         <v>8.398</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>20.38284</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="8" t="n">
         <v>20.3828</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H24" s="8" t="n">
         <v>20.383</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I24" s="8" t="n">
         <v>20.383</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="9" t="n">
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="10" t="n">
         <v>247872.087</v>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" s="10" t="n">
         <v>920742.703</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>8.87922</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="8" t="n">
         <v>3.412</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="8" t="n">
         <v>5.4672</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H28" s="8" t="n">
         <v>8.879</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I28" s="8" t="n">
         <v>8.879</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="6" t="n">
+      <c r="D29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="7" t="n">
         <v>277.73442</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="8" t="n">
         <v>97.044</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="8" t="n">
         <v>180.6904</v>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="H29" s="8" t="n">
         <v>2221.875</v>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="I29" s="8" t="n">
         <v>4443.751</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="6" t="n">
+      <c r="D30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="7" t="n">
         <v>466.32672</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="8" t="n">
         <v>97.044</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="8" t="n">
         <v>369.2827</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H30" s="8" t="n">
         <v>3730.614</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="8" t="n">
         <v>7461.228</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="6" t="n">
+      <c r="D31" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="7" t="n">
         <v>42.92352</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="8" t="n">
         <v>9.098</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="8" t="n">
         <v>33.8255</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="H31" s="8" t="n">
         <v>343.388</v>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="I31" s="8" t="n">
         <v>686.776</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="6" t="n">
+      <c r="D32" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="7" t="n">
         <v>75.17448</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="8" t="n">
         <v>18.196</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="8" t="n">
         <v>56.9785</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H32" s="8" t="n">
         <v>601.396</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="I32" s="8" t="n">
         <v>1202.792</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="7" t="n">
         <v>5345.99028</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="8" t="n">
         <v>433.668</v>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="8" t="n">
         <v>4912.3223</v>
       </c>
-      <c r="H33" s="7" t="n">
+      <c r="H33" s="8" t="n">
         <v>342143.378</v>
       </c>
-      <c r="I33" s="7" t="n">
+      <c r="I33" s="8" t="n">
         <v>1368573.512</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>0.26244</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="8" t="n">
         <v>0.2624</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="H34" s="8" t="n">
         <v>16.796</v>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="I34" s="8" t="n">
         <v>67.185</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="7" t="n">
         <v>0.26244</v>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="8" t="n">
         <v>0.2624</v>
       </c>
-      <c r="H35" s="7" t="n">
+      <c r="H35" s="8" t="n">
         <v>4.199</v>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="I35" s="8" t="n">
         <v>8.398</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>1.77876</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="8" t="n">
         <v>1.7788</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="H36" s="8" t="n">
         <v>1.779</v>
       </c>
-      <c r="I36" s="7" t="n">
+      <c r="I36" s="8" t="n">
         <v>1.779</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="9" t="n">
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="10" t="n">
         <v>349072.304</v>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="I37" s="10" t="n">
         <v>1382454.299</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>9.7686</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="8" t="n">
         <v>4.17</v>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="8" t="n">
         <v>5.5986</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H40" s="8" t="n">
         <v>9.769</v>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="I40" s="8" t="n">
         <v>9.769</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="n">
+      <c r="B41" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="7" t="n">
         <v>4.18446</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="8" t="n">
         <v>4.1845</v>
       </c>
-      <c r="H41" s="7" t="n">
+      <c r="H41" s="8" t="n">
         <v>4.184</v>
       </c>
-      <c r="I41" s="7" t="n">
+      <c r="I41" s="8" t="n">
         <v>4.184</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="6" t="n">
+      <c r="D42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="7" t="n">
         <v>366.11838</v>
       </c>
-      <c r="F42" s="7" t="n">
+      <c r="F42" s="8" t="n">
         <v>97.044</v>
       </c>
-      <c r="G42" s="7" t="n">
+      <c r="G42" s="8" t="n">
         <v>269.0744</v>
       </c>
-      <c r="H42" s="7" t="n">
+      <c r="H42" s="8" t="n">
         <v>2928.947</v>
       </c>
-      <c r="I42" s="7" t="n">
+      <c r="I42" s="8" t="n">
         <v>5857.894</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="4" t="n">
+      <c r="B43" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="6" t="n">
+      <c r="D43" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="7" t="n">
         <v>332.68644</v>
       </c>
-      <c r="F43" s="7" t="n">
+      <c r="F43" s="8" t="n">
         <v>97.044</v>
       </c>
-      <c r="G43" s="7" t="n">
+      <c r="G43" s="8" t="n">
         <v>235.6424</v>
       </c>
-      <c r="H43" s="7" t="n">
+      <c r="H43" s="8" t="n">
         <v>2661.492</v>
       </c>
-      <c r="I43" s="7" t="n">
+      <c r="I43" s="8" t="n">
         <v>5322.983</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="6" t="n">
+      <c r="D44" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="7" t="n">
         <v>41.9904</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="8" t="n">
         <v>9.098</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="8" t="n">
         <v>32.8924</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H44" s="8" t="n">
         <v>335.923</v>
       </c>
-      <c r="I44" s="7" t="n">
+      <c r="I44" s="8" t="n">
         <v>671.846</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="4" t="n">
+      <c r="B45" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="6" t="n">
+      <c r="D45" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="7" t="n">
         <v>68.58432</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="8" t="n">
         <v>18.196</v>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="8" t="n">
         <v>50.3883</v>
       </c>
-      <c r="H45" s="7" t="n">
+      <c r="H45" s="8" t="n">
         <v>548.675</v>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="I45" s="8" t="n">
         <v>1097.349</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D46" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="6" t="n">
+      <c r="D46" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="7" t="n">
         <v>1226.6883</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="8" t="n">
         <v>1226.6883</v>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="H46" s="8" t="n">
         <v>9813.506</v>
       </c>
-      <c r="I46" s="7" t="n">
+      <c r="I46" s="8" t="n">
         <v>19627.013</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="4" t="n">
+      <c r="B47" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D47" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="6" t="n">
+      <c r="D47" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="7" t="n">
         <v>1070.7552</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="8" t="n">
         <v>1070.7552</v>
       </c>
-      <c r="H47" s="7" t="n">
+      <c r="H47" s="8" t="n">
         <v>8566.042</v>
       </c>
-      <c r="I47" s="7" t="n">
+      <c r="I47" s="8" t="n">
         <v>17132.083</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="7" t="n">
         <v>5204.92878</v>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="F48" s="8" t="n">
         <v>435.184</v>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="8" t="n">
         <v>4769.7448</v>
       </c>
-      <c r="H48" s="7" t="n">
+      <c r="H48" s="8" t="n">
         <v>333115.442</v>
       </c>
-      <c r="I48" s="7" t="n">
+      <c r="I48" s="8" t="n">
         <v>1332461.768</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="4" t="n">
+      <c r="B49" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="7" t="n">
         <v>0.26244</v>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="G49" s="8" t="n">
         <v>0.2624</v>
       </c>
-      <c r="H49" s="7" t="n">
+      <c r="H49" s="8" t="n">
         <v>16.796</v>
       </c>
-      <c r="I49" s="7" t="n">
+      <c r="I49" s="8" t="n">
         <v>67.185</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="7" t="n">
         <v>0.26244</v>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F50" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G50" s="8" t="n">
         <v>0.2624</v>
       </c>
-      <c r="H50" s="7" t="n">
+      <c r="H50" s="8" t="n">
         <v>4.199</v>
       </c>
-      <c r="I50" s="7" t="n">
+      <c r="I50" s="8" t="n">
         <v>8.398</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" s="7" t="n">
         <v>3.47004</v>
       </c>
-      <c r="F51" s="7" t="n">
+      <c r="F51" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="G51" s="8" t="n">
         <v>3.47</v>
       </c>
-      <c r="H51" s="7" t="n">
+      <c r="H51" s="8" t="n">
         <v>3.47</v>
       </c>
-      <c r="I51" s="7" t="n">
+      <c r="I51" s="8" t="n">
         <v>3.47</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="9" t="n">
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="10" t="n">
         <v>358008.445</v>
       </c>
-      <c r="I52" s="9" t="n">
+      <c r="I52" s="10" t="n">
         <v>1382263.942</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="54" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="9" t="n">
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>8.87922</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>3.412</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>5.4672</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>8.879</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>8.879</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>277.73442</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>97.044</v>
+      </c>
+      <c r="G56" s="8" t="n">
+        <v>180.6904</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>2221.875</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>4443.751</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>616.2237</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>97.044</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>519.1792</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>4929.79</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>9859.579</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>42.92352</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>9.098</v>
+      </c>
+      <c r="G58" s="8" t="n">
+        <v>33.8255</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>343.388</v>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>686.776</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B59" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>75.17448</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>18.196</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>56.9785</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>601.396</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>1202.792</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>5148.89784</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>436.7</v>
+      </c>
+      <c r="G60" s="8" t="n">
+        <v>4712.1977</v>
+      </c>
+      <c r="H60" s="8" t="n">
+        <v>329529.462</v>
+      </c>
+      <c r="I60" s="8" t="n">
+        <v>1318117.847</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>16.796</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>67.185</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>4.199</v>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>8.398</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>4.75308</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>4.7531</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>4.753</v>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>4.753</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="10" t="n">
+        <v>337660.538</v>
+      </c>
+      <c r="I64" s="10" t="n">
+        <v>1334399.96</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="10" t="n">
         <v>0.9905</v>
       </c>
-      <c r="I54" s="9" t="n">
+      <c r="I66" s="10" t="n">
         <v>0.931</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="9" t="n">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="10" t="n">
         <v>1.3949</v>
       </c>
-      <c r="I55" s="9" t="n">
+      <c r="I67" s="10" t="n">
         <v>1.3978</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="9" t="n">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="10" t="n">
         <v>1.4307</v>
       </c>
-      <c r="I56" s="9" t="n">
+      <c r="I68" s="10" t="n">
         <v>1.3976</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="9" t="n">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="10" t="n">
         <v>1.0256</v>
       </c>
-      <c r="I57" s="9" t="n">
+      <c r="I69" s="10" t="n">
         <v>0.9999</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="10" t="n">
+        <v>1.3493</v>
+      </c>
+      <c r="I70" s="10" t="n">
+        <v>1.3492</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="10" t="n">
+        <v>0.9673</v>
+      </c>
+      <c r="I71" s="10" t="n">
+        <v>0.9652</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="17">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B12:G12"/>
@@ -1641,10 +1956,14 @@
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B68:G68"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
